--- a/Employee_Reports_wi52/Dushan Priyankara Herath Herath Mudiyanselage Q0578.xlsx
+++ b/Employee_Reports_wi52/Dushan Priyankara Herath Herath Mudiyanselage Q0578.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-106</v>
+        <v>-114</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-98</v>
+        <v>-106</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-97</v>
+        <v>-105</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-93</v>
+        <v>-101</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-84</v>
+        <v>-92</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-86</v>
+        <v>-94</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-72</v>
+        <v>-80</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-99</v>
+        <v>-107</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-79</v>
+        <v>-87</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-322</v>
+        <v>-330</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1265,11 +1265,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-420</v>
+        <v>-428</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-443</v>
+        <v>-451</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-385</v>
+        <v>-393</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1400,11 +1400,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-385</v>
+        <v>-393</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1437,11 +1437,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-157</v>
+        <v>-165</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-157</v>
+        <v>-165</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1535,11 +1535,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-182</v>
+        <v>-190</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1584,11 +1584,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-53</v>
+        <v>-61</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-28</v>
+        <v>-36</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-28</v>
+        <v>-36</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1731,11 +1731,11 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -1780,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -1817,11 +1817,11 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1866,11 +1866,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1881,41 +1881,41 @@
       <c r="K30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr"/>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>26-Aug-2024</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>26-Aug-2026</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr"/>
+      <c r="H31" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
